--- a/architecture/released/v1.1/RELEASE-MANIFEST-v1.1.xlsx
+++ b/architecture/released/v1.1/RELEASE-MANIFEST-v1.1.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Manifest" sheetId="1" r:id="R1c7aef08dd7a4cb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Manifest" sheetId="1" r:id="Rb0b9cc3d6cbb4f07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -141,17 +141,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReleaseManifestv1_1" displayName="ReleaseManifestv1_1" ref="A5:H38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:H38"/>
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReleaseManifestv1_1" displayName="ReleaseManifestv1_1" ref="A5:J46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:J46"/>
+  <x:tableColumns count="10">
     <x:tableColumn id="1" name="Relative Path"/>
     <x:tableColumn id="2" name="Document Identifier"/>
     <x:tableColumn id="3" name="Document Title"/>
     <x:tableColumn id="4" name="Semantic Version"/>
     <x:tableColumn id="5" name="Status"/>
-    <x:tableColumn id="6" name="SHA-256 Checksum"/>
-    <x:tableColumn id="7" name="Superseded Document"/>
-    <x:tableColumn id="8" name="Approval Reference"/>
+    <x:tableColumn id="6" name="Current"/>
+    <x:tableColumn id="7" name="Authority"/>
+    <x:tableColumn id="8" name="SHA-256 Checksum"/>
+    <x:tableColumn id="9" name="Superseded Document"/>
+    <x:tableColumn id="10" name="Approval Reference"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -357,9 +359,11 @@
     <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="68" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="35" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="68" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="35" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -373,6 +377,8 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
@@ -385,6 +391,8 @@
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="7"/>
       <x:c r="H2" s="7"/>
+      <x:c r="I2" s="7"/>
+      <x:c r="J2" s="7"/>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="10" t="str">
@@ -397,7 +405,7 @@
         <x:v>Artifact Count</x:v>
       </x:c>
       <x:c r="D3" s="10" t="n">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E3" s="10" t="str">
         <x:v>Generated: 2026-08-08 | SHA-256 lowercase hexadecimal</x:v>
@@ -405,6 +413,8 @@
       <x:c r="F3" s="10"/>
       <x:c r="G3" s="10"/>
       <x:c r="H3" s="10"/>
+      <x:c r="I3" s="10"/>
+      <x:c r="J3" s="10"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="15" t="str">
@@ -423,12 +433,18 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str">
+        <x:v>Current</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="str">
+        <x:v>Authority</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="str">
         <x:v>SHA-256 Checksum</x:v>
       </x:c>
-      <x:c r="G5" s="15" t="str">
+      <x:c r="I5" s="15" t="str">
         <x:v>Superseded Document</x:v>
       </x:c>
-      <x:c r="H5" s="15" t="str">
+      <x:c r="J5" s="15" t="str">
         <x:v>Approval Reference</x:v>
       </x:c>
     </x:row>
@@ -448,13 +464,19 @@
       <x:c r="E6" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F6" s="20" t="str">
+      <x:c r="F6" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="str">
         <x:v>3a6958b84a55e125c5a9384bed04a31ae9389040c796c2685f18b6b39b8eb542</x:v>
       </x:c>
-      <x:c r="G6" s="17" t="str">
+      <x:c r="I6" s="17" t="str">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="H6" s="17" t="str">
+      <x:c r="J6" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
@@ -474,11 +496,17 @@
       <x:c r="E7" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F7" s="20" t="str">
+      <x:c r="F7" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G7" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H7" s="20" t="str">
         <x:v>c98ff6b4db36f31b0c6d495333678f28dd27272b39f444bb9f81a632a95dce93</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="str"/>
-      <x:c r="H7" s="17" t="str">
+      <x:c r="I7" s="17" t="str"/>
+      <x:c r="J7" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
@@ -498,11 +526,17 @@
       <x:c r="E8" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F8" s="20" t="str">
+      <x:c r="F8" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G8" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H8" s="20" t="str">
         <x:v>882b1a45a9502763e6bb4e49d722ff07f8c3a0e7f0e3cfe87c92313f52c9a8b7</x:v>
       </x:c>
-      <x:c r="G8" s="17" t="str"/>
-      <x:c r="H8" s="17" t="str">
+      <x:c r="I8" s="17" t="str"/>
+      <x:c r="J8" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
@@ -522,733 +556,913 @@
       <x:c r="E9" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F9" s="20" t="str">
+      <x:c r="F9" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H9" s="20" t="str">
         <x:v>0a8ebb468670c9311afc66ffa055bd8c2aa261ca9a4f949f8afdfa454667157f</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="str"/>
-      <x:c r="H9" s="17" t="str">
+      <x:c r="I9" s="17" t="str"/>
+      <x:c r="J9" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="17" t="str">
-        <x:v>architecture/released/v1.1/ARCHITECTURE-GLOSSARY-v1.0_FROZEN.md</x:v>
+        <x:v>architecture/released/v1.1/ARCHITECTURE-CONSISTENCY-REPORT-v1.2_FROZEN.md</x:v>
       </x:c>
       <x:c r="B10" s="17" t="str">
-        <x:v>Architecture Glossary</x:v>
+        <x:v>Architecture Consistency Report</x:v>
       </x:c>
       <x:c r="C10" s="17" t="str">
-        <x:v>ARCHITECTURE-GLOSSARY-v1.0</x:v>
+        <x:v>ARCHITECTURE-CONSISTENCY-REPORT-v1.2</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E10" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F10" s="20" t="str">
-        <x:v>7da811d8832e98bf7d86346aed7b9c0a2aa0ee712118d70882f6d54c95ad719b</x:v>
-      </x:c>
-      <x:c r="G10" s="17" t="str"/>
-      <x:c r="H10" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F10" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G10" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="str">
+        <x:v>9fc27c56c45050e56e2c21c2d7a91ab14d61a9b43f98e732984d0cf2e3d6aeda</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J10" s="17" t="str">
+        <x:v>ECOM Architecture Governance release approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="17" t="str">
-        <x:v>architecture/released/v1.1/ASM-001_Assertion_Business_Capability_Specification_v2.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ARCHITECTURE-DRIFT-REPORT-v1.2_FROZEN.md</x:v>
       </x:c>
       <x:c r="B11" s="17" t="str">
-        <x:v>ASM-001</x:v>
+        <x:v>Architecture Drift Report</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
-        <x:v>ASM-001 Assertion Business Capability Specification</x:v>
+        <x:v>ARCHITECTURE-DRIFT-REPORT-v1.2</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F11" s="20" t="str">
-        <x:v>35171f4bb76502ddc8f32810550e9493e4d6be34a4d65e813a83588408fb9e92</x:v>
-      </x:c>
-      <x:c r="G11" s="17" t="str">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="H11" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F11" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G11" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="str">
+        <x:v>ae984515f2d652a14bc03269ac08d1a783a033ed740357e2e466629a99019622</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J11" s="17" t="str">
+        <x:v>ECOM Architecture Governance release approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="17" t="str">
-        <x:v>architecture/released/v1.1/CAM-001_Canonical_Projection_Model_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ARCHITECTURE-GLOSSARY-v1.1_FROZEN.md</x:v>
       </x:c>
       <x:c r="B12" s="17" t="str">
-        <x:v>CAM-001</x:v>
+        <x:v>Architecture Glossary</x:v>
       </x:c>
       <x:c r="C12" s="17" t="str">
-        <x:v>CAM-001 Canonical Projection Model</x:v>
+        <x:v>ARCHITECTURE-GLOSSARY-v1.1</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F12" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G12" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H12" s="20" t="str">
+        <x:v>4aa16383b0dc281f4a9475725d011e4e9dfc6c7ca19adcc9475ef7b5cb46fea0</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="E12" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F12" s="20" t="str">
-        <x:v>1ae6280a0b7ed79ba182b736c87ff55e9da225700dc2ded90b3a043f699f9c65</x:v>
-      </x:c>
-      <x:c r="G12" s="17" t="str"/>
-      <x:c r="H12" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="J12" s="17" t="str">
+        <x:v>RND-001 registry normalization approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="17" t="str">
-        <x:v>architecture/released/v1.1/CDD_TEMPLATE_v2.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ASM-001_Assertion_Business_Capability_Specification_v2.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B13" s="17" t="str">
-        <x:v>CDD Template</x:v>
+        <x:v>ASM-001</x:v>
       </x:c>
       <x:c r="C13" s="17" t="str">
-        <x:v>CDD TEMPLATE</x:v>
+        <x:v>ASM-001 Assertion Business Capability Specification</x:v>
       </x:c>
       <x:c r="D13" s="19" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F13" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G13" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H13" s="20" t="str">
+        <x:v>9e78c22a316a3573486f4bb034dcadac1816e09f87f12f3e8680c45d6e968fa9</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
         <x:v>2.1</x:v>
       </x:c>
-      <x:c r="E13" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F13" s="20" t="str">
-        <x:v>34bcaa1f37d166120e82ecff1a713057cd8c14bbf294f743e8c0cedb5a9e88e4</x:v>
-      </x:c>
-      <x:c r="G13" s="17" t="str">
-        <x:v>CDD Template v2.0</x:v>
-      </x:c>
-      <x:c r="H13" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="J13" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="17" t="str">
-        <x:v>architecture/released/v1.1/CDD-003-Revision-2-Complete-Canonical-Enterprise-Ontology.md</x:v>
+        <x:v>architecture/released/v1.1/BASELINE-RECORD-v1.3_FROZEN.md</x:v>
       </x:c>
       <x:c r="B14" s="17" t="str">
-        <x:v>CDD-003 Revision 2</x:v>
+        <x:v>Baseline Record</x:v>
       </x:c>
       <x:c r="C14" s="17" t="str">
-        <x:v>CDD-003-Revision-2-Complete-Canonical-Enterprise-Ontology</x:v>
+        <x:v>BASELINE-RECORD-v1.3</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>2.0</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E14" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F14" s="20" t="str">
-        <x:v>5da8fe484872ddc3e4d8ee2c210e06268159a6394b0d2948d7a47a8298ea43a2</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="str">
-        <x:v>CDD-003 Foundation Reference Model</x:v>
-      </x:c>
-      <x:c r="H14" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F14" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="str">
+        <x:v>58194e9b2e1c643721e278e09a62d9aa77a5398595cc0b511bb21130fa16472d</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>Baseline Record v1.2</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="str">
+        <x:v>RND-001 registry normalization approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="17" t="str">
-        <x:v>architecture/released/v1.1/CDS-001_Codex_Development_Standard_v1.3_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/CAM-001_Canonical_Projection_Model_v1.1_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B15" s="17" t="str">
-        <x:v>CDS-001</x:v>
+        <x:v>CAM-001</x:v>
       </x:c>
       <x:c r="C15" s="17" t="str">
-        <x:v>CDS-001 Codex Development Standard</x:v>
+        <x:v>CAM-001 Canonical Projection Model</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="E15" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F15" s="20" t="str">
-        <x:v>0668248d409fa5916e90cec5e811dc00b639d762abc16c2e8e021dcd9194349a</x:v>
-      </x:c>
-      <x:c r="G15" s="17" t="str">
-        <x:v>CDS-001 v1.2 and Authorized Artifacts Amendment</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F15" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H15" s="20" t="str">
+        <x:v>675168c7d0faf552200ae3a2ab023df1a49e37d4525770d6e78af31a463e418d</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="J15" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="17" t="str">
-        <x:v>architecture/released/v1.1/DRM-001_Decision_Business_Capability_Specification_v1.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/CDD_TEMPLATE_v2.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B16" s="17" t="str">
-        <x:v>DRM-001</x:v>
+        <x:v>CDD Template</x:v>
       </x:c>
       <x:c r="C16" s="17" t="str">
-        <x:v>DRM-001 Decision Business Capability Specification</x:v>
+        <x:v>CDD TEMPLATE</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
-        <x:v>1.1</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="E16" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F16" s="20" t="str">
-        <x:v>20c0500dea5521f7fface35b3424aba4f1346460735b5217b38f5fc6713fb419</x:v>
-      </x:c>
-      <x:c r="G16" s="17" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="H16" s="17" t="str">
+      <x:c r="F16" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G16" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H16" s="20" t="str">
+        <x:v>4abe2ace1e631d53321fe3e8022e54096833a4be4ea672af0f67c05d64203cf2</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>CDD Template v2.1</x:v>
+      </x:c>
+      <x:c r="J16" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="17" t="str">
-        <x:v>architecture/released/v1.1/EAD-001_Enterprise_Attribute_Dictionary_v1_3.xlsx</x:v>
+        <x:v>architecture/released/v1.1/CDD-003-Revision-2-Complete-Canonical-Enterprise-Ontology.md</x:v>
       </x:c>
       <x:c r="B17" s="17" t="str">
-        <x:v>EAD-001</x:v>
+        <x:v>CDD-003 Revision 2</x:v>
       </x:c>
       <x:c r="C17" s="17" t="str">
-        <x:v>EAD-001 Enterprise Attribute Dictionary</x:v>
+        <x:v>CDD-003-Revision-2-Complete-Canonical-Enterprise-Ontology</x:v>
       </x:c>
       <x:c r="D17" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>2.0</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>Development</x:v>
-      </x:c>
-      <x:c r="F17" s="20" t="str">
-        <x:v>121d6b33566246653765077589e524b43907d547e890284fef3caeda94b1f1df</x:v>
-      </x:c>
-      <x:c r="G17" s="17" t="str">
-        <x:v>Earlier attribute dictionaries</x:v>
-      </x:c>
-      <x:c r="H17" s="17" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F17" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G17" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H17" s="20" t="str">
+        <x:v>5da8fe484872ddc3e4d8ee2c210e06268159a6394b0d2948d7a47a8298ea43a2</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="str">
+        <x:v>CDD-003 Foundation Reference Model</x:v>
+      </x:c>
+      <x:c r="J17" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="17" t="str">
-        <x:v>architecture/released/v1.1/EAH-001_ECOM_Architecture_Handbook_v1.3_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/CDD-AUTHORIZATION-GAP-REVIEW-v1.1_FROZEN.md</x:v>
       </x:c>
       <x:c r="B18" s="17" t="str">
-        <x:v>EAH-001</x:v>
+        <x:v>CDD Authorization Gap Review</x:v>
       </x:c>
       <x:c r="C18" s="17" t="str">
-        <x:v>EAH-001 ECOM Architecture Handbook</x:v>
+        <x:v>CDD-AUTHORIZATION-GAP-REVIEW-v1.1</x:v>
       </x:c>
       <x:c r="D18" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F18" s="20" t="str">
-        <x:v>2290ddd0850e6a4797db831112a9c39a838b7e00aecf5c7877d38935dea442fe</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="str">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="H18" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F18" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H18" s="20" t="str">
+        <x:v>24d83e6452e218983ff8de3e11ec5ce4857e81da950a9b2be7a212038c69ba65</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="str">
+        <x:v>RND-001 registry normalization approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" s="17" t="str">
-        <x:v>architecture/released/v1.1/ECOM_Logical_Data_Model_v1_3.md</x:v>
+        <x:v>architecture/released/v1.1/CDS-001_Codex_Development_Standard_v1.3_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B19" s="17" t="str">
-        <x:v>ECOM Logical Data Model</x:v>
+        <x:v>CDS-001</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
-        <x:v>ECOM Logical Data Model</x:v>
+        <x:v>CDS-001 Codex Development Standard</x:v>
       </x:c>
       <x:c r="D19" s="19" t="str">
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
-        <x:v>Development</x:v>
-      </x:c>
-      <x:c r="F19" s="20" t="str">
-        <x:v>b5c2d2fea44ecdbb365297f7877d7db457fdade73b108581ee5ef9ade81a0b3c</x:v>
-      </x:c>
-      <x:c r="G19" s="17" t="str">
-        <x:v>Earlier logical models</x:v>
-      </x:c>
-      <x:c r="H19" s="17" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G19" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H19" s="20" t="str">
+        <x:v>0668248d409fa5916e90cec5e811dc00b639d762abc16c2e8e021dcd9194349a</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="str">
+        <x:v>CDS-001 v1.2 and Authorized Artifacts Amendment</x:v>
+      </x:c>
+      <x:c r="J19" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" s="17" t="str">
-        <x:v>architecture/released/v1.1/ECOM_Physical_Data_Model_v1_3.sql</x:v>
+        <x:v>architecture/released/v1.1/DEPENDENCY-MATRIX-v1.1.csv</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>ECOM Physical Data Model</x:v>
+        <x:v>Architecture Dependency Matrix</x:v>
       </x:c>
       <x:c r="C20" s="17" t="str">
-        <x:v>ECOM Physical Data Model</x:v>
+        <x:v>DEPENDENCY-MATRIX-v1.1.csv</x:v>
       </x:c>
       <x:c r="D20" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F20" s="20" t="str">
-        <x:v>9242abdd3de19f7a2c33f406e71d50ad629132dfe783375d864a7fcb2f90cd2b</x:v>
-      </x:c>
-      <x:c r="G20" s="17" t="str">
-        <x:v>Earlier physical models</x:v>
-      </x:c>
-      <x:c r="H20" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F20" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G20" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H20" s="20" t="str">
+        <x:v>16ff8f4f4bcdbcfe90e78404bef10a751c59e5c8ac5ebef932f2edebd784db7d</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str"/>
+      <x:c r="J20" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" s="17" t="str">
-        <x:v>architecture/released/v1.1/EIC-001_Cognitive_Engine_Invocation_Architecture_v1.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/DEPENDENCY-RESOLUTION-REPORT-v1.0_FROZEN.md</x:v>
       </x:c>
       <x:c r="B21" s="17" t="str">
-        <x:v>EIC-001</x:v>
+        <x:v>Dependency Resolution Report</x:v>
       </x:c>
       <x:c r="C21" s="17" t="str">
-        <x:v>EIC-001 Cognitive Engine Invocation Architecture</x:v>
+        <x:v>DEPENDENCY-RESOLUTION-REPORT-v1.0</x:v>
       </x:c>
       <x:c r="D21" s="19" t="str">
-        <x:v>1.1</x:v>
+        <x:v>1.0</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F21" s="20" t="str">
-        <x:v>1c0c6d12ae6c495f00b41c2104ea629aadb535f7ce42b0262e48c265fb8c6abe</x:v>
-      </x:c>
-      <x:c r="G21" s="17" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="H21" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F21" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G21" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H21" s="20" t="str">
+        <x:v>7ae32d3b33b9a80c419cd2ec5b715106570e74d0a65484949bb3ad17cc27deae</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str"/>
+      <x:c r="J21" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="17" t="str">
-        <x:v>architecture/released/v1.1/EOM-001_Cognitive_Engine_Orchestration_Architecture_v1.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/DRM-001_Decision_Business_Capability_Specification_v1.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B22" s="17" t="str">
-        <x:v>EOM-001</x:v>
+        <x:v>DRM-001</x:v>
       </x:c>
       <x:c r="C22" s="17" t="str">
-        <x:v>EOM-001 Cognitive Engine Orchestration Architecture</x:v>
+        <x:v>DRM-001 Decision Business Capability Specification</x:v>
       </x:c>
       <x:c r="D22" s="19" t="str">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H22" s="20" t="str">
+        <x:v>6ce163a86d76aaf8d849f8eb041740e536fb7c46718b838e4485e98a62625423</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="E22" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F22" s="20" t="str">
-        <x:v>c23b29b90e83aab0d1c14404af818cc89acd9730ee2d496a04667cbbfdd6c87a</x:v>
-      </x:c>
-      <x:c r="G22" s="17" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="H22" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="J22" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" s="17" t="str">
-        <x:v>architecture/released/v1.1/ERM-001_Enterprise_Entity_Resolution_Business_Capability_Specification_v2.2_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/EAD-001_Enterprise_Attribute_Dictionary_v1_3.xlsx</x:v>
       </x:c>
       <x:c r="B23" s="17" t="str">
-        <x:v>ERM-001</x:v>
+        <x:v>EAD-001</x:v>
       </x:c>
       <x:c r="C23" s="17" t="str">
-        <x:v>ERM-001 Enterprise Entity Resolution Business Capability Specification</x:v>
+        <x:v>EAD-001 Enterprise Attribute Dictionary</x:v>
       </x:c>
       <x:c r="D23" s="19" t="str">
-        <x:v>2.2</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F23" s="20" t="str">
-        <x:v>e04f5cc4987e30e147e6540ad489c2921bde44ae30301c297c15c916ed98cb03</x:v>
-      </x:c>
-      <x:c r="G23" s="17" t="str">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="H23" s="17" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G23" s="18" t="str">
+        <x:v>NON-AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H23" s="20" t="str">
+        <x:v>121d6b33566246653765077589e524b43907d547e890284fef3caeda94b1f1df</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="str"/>
+      <x:c r="J23" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" s="17" t="str">
-        <x:v>architecture/released/v1.1/ESM-001_Cognitive_Engine_Execution_State_Architecture_v1.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/EAH-001_ECOM_Architecture_Handbook_v1.4_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B24" s="17" t="str">
-        <x:v>ESM-001</x:v>
+        <x:v>EAH-001</x:v>
       </x:c>
       <x:c r="C24" s="17" t="str">
-        <x:v>ESM-001 Cognitive Engine Execution State Architecture</x:v>
+        <x:v>EAH-001 ECOM Architecture Handbook</x:v>
       </x:c>
       <x:c r="D24" s="19" t="str">
-        <x:v>1.1</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="E24" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F24" s="20" t="str">
-        <x:v>18b444d8e1c2c5b21c12c45a797973bea066283817ace847b549bd14f4b72578</x:v>
-      </x:c>
-      <x:c r="G24" s="17" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="H24" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F24" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H24" s="20" t="str">
+        <x:v>6d71168bc4cbdba5c87ce16121e06977c81e5072791d7c0d0d4e251ec1cdf2c0</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J24" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" s="17" t="str">
-        <x:v>architecture/released/v1.1/GEM-001_Governance_Exception_Business_Specification_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ECOM_Logical_Data_Model_v1_3.md</x:v>
       </x:c>
       <x:c r="B25" s="17" t="str">
-        <x:v>GEM-001</x:v>
+        <x:v>ECOM Logical Data Model</x:v>
       </x:c>
       <x:c r="C25" s="17" t="str">
-        <x:v>GEM-001 Governance Exception Business Specification</x:v>
+        <x:v>ECOM Logical Data Model</x:v>
       </x:c>
       <x:c r="D25" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E25" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F25" s="20" t="str">
-        <x:v>84c45b69ef9afb01ee32775750b09f6e2e118a98a6effd2d329a87e66f70e35e</x:v>
-      </x:c>
-      <x:c r="G25" s="17" t="str"/>
-      <x:c r="H25" s="17" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="str">
+        <x:v>NON-AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H25" s="20" t="str">
+        <x:v>b5c2d2fea44ecdbb365297f7877d7db457fdade73b108581ee5ef9ade81a0b3c</x:v>
+      </x:c>
+      <x:c r="I25" s="17" t="str"/>
+      <x:c r="J25" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" s="17" t="str">
-        <x:v>architecture/released/v1.1/GRM-001_Governance_Business_Capability_Specification_v1.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ECOM_Physical_Data_Model_v1_3.sql</x:v>
       </x:c>
       <x:c r="B26" s="17" t="str">
-        <x:v>GRM-001</x:v>
+        <x:v>ECOM Physical Data Model</x:v>
       </x:c>
       <x:c r="C26" s="17" t="str">
-        <x:v>GRM-001 Governance Business Capability Specification</x:v>
+        <x:v>ECOM Physical Data Model</x:v>
       </x:c>
       <x:c r="D26" s="19" t="str">
-        <x:v>1.1</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="E26" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F26" s="20" t="str">
-        <x:v>da290fd2bb521b278f9a245a8111da9eeddd6fec817596bdc6c57d68d1bffff3</x:v>
-      </x:c>
-      <x:c r="G26" s="17" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="H26" s="17" t="str">
+      <x:c r="F26" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G26" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H26" s="20" t="str">
+        <x:v>9242abdd3de19f7a2c33f406e71d50ad629132dfe783375d864a7fcb2f90cd2b</x:v>
+      </x:c>
+      <x:c r="I26" s="17" t="str">
+        <x:v>Earlier physical models</x:v>
+      </x:c>
+      <x:c r="J26" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" s="17" t="str">
-        <x:v>architecture/released/v1.1/KRM-001_Knowledge_Business_Capability_Specification_v1.3_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/EIC-001_Cognitive_Engine_Invocation_Architecture_v1.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B27" s="17" t="str">
-        <x:v>KRM-001</x:v>
+        <x:v>EIC-001</x:v>
       </x:c>
       <x:c r="C27" s="17" t="str">
-        <x:v>KRM-001 Knowledge Business Capability Specification</x:v>
+        <x:v>EIC-001 Cognitive Engine Invocation Architecture</x:v>
       </x:c>
       <x:c r="D27" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E27" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F27" s="20" t="str">
-        <x:v>9b276dc8cf99e3aac3284717edc78991570f849589a748672b7da496b65fe832</x:v>
-      </x:c>
-      <x:c r="G27" s="17" t="str">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="H27" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F27" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G27" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H27" s="20" t="str">
+        <x:v>571775a8b4e250492fee8dedee1875041e14ea7e625d44cd1d1405e6263bd4c3</x:v>
+      </x:c>
+      <x:c r="I27" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J27" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" s="17" t="str">
-        <x:v>architecture/released/v1.1/PAD-001_Product_Access_Protocol_Specification_v1.3_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/EOM-001_Cognitive_Engine_Orchestration_Architecture_v1.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B28" s="17" t="str">
-        <x:v>PAD-001</x:v>
+        <x:v>EOM-001</x:v>
       </x:c>
       <x:c r="C28" s="17" t="str">
-        <x:v>PAD-001 Product Access Protocol Specification</x:v>
+        <x:v>EOM-001 Cognitive Engine Orchestration Architecture</x:v>
       </x:c>
       <x:c r="D28" s="19" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E28" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F28" s="20" t="str">
-        <x:v>2a11906e0c759c787f0a6dfc1c2cc9810e34a097aad4a8b4dca2c3f2e599ad06</x:v>
-      </x:c>
-      <x:c r="G28" s="17" t="str">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="H28" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F28" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G28" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H28" s="20" t="str">
+        <x:v>0bbca2f658693392db276794ecfbec57693adfe283db4b16eab96640614a7bb6</x:v>
+      </x:c>
+      <x:c r="I28" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J28" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" s="17" t="str">
-        <x:v>architecture/released/v1.1/PMM-001_Persistence_Role_Mapping_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/ERM-001_Enterprise_Entity_Resolution_Business_Capability_Specification_v2.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B29" s="17" t="str">
-        <x:v>PMM-001</x:v>
+        <x:v>ERM-001</x:v>
       </x:c>
       <x:c r="C29" s="17" t="str">
-        <x:v>PMM-001 Persistence Role Mapping</x:v>
+        <x:v>ERM-001 Enterprise Entity Resolution Business Capability Specification</x:v>
       </x:c>
       <x:c r="D29" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="E29" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F29" s="20" t="str">
-        <x:v>1dda16a421594975a32bd3aa57cdf8aeb4273d1f9abb48a2f3add6f615585648</x:v>
-      </x:c>
-      <x:c r="G29" s="17" t="str"/>
-      <x:c r="H29" s="17" t="str">
+      <x:c r="F29" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H29" s="20" t="str">
+        <x:v>e04f5cc4987e30e147e6540ad489c2921bde44ae30301c297c15c916ed98cb03</x:v>
+      </x:c>
+      <x:c r="I29" s="17" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="J29" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" s="17" t="str">
-        <x:v>architecture/released/v1.1/README.md</x:v>
+        <x:v>architecture/released/v1.1/ESM-001_Cognitive_Engine_Execution_State_Architecture_v1.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B30" s="17" t="str">
-        <x:v>RELEASE-README</x:v>
+        <x:v>ESM-001</x:v>
       </x:c>
       <x:c r="C30" s="17" t="str">
-        <x:v>Architecture Release Baseline README</x:v>
+        <x:v>ESM-001 Cognitive Engine Execution State Architecture</x:v>
       </x:c>
       <x:c r="D30" s="19" t="str">
-        <x:v>v1.1</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E30" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F30" s="20" t="str">
-        <x:v>0b01420bb87741ec1fbcdfcdcb0a7ff89e521652bb20008fbc77e29d41ddcb1f</x:v>
-      </x:c>
-      <x:c r="G30" s="17" t="str"/>
-      <x:c r="H30" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F30" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G30" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H30" s="20" t="str">
+        <x:v>6d8f87c9545ca500053d444f5f8ac24640dc98cae173b5c01ab7d28a43c10079</x:v>
+      </x:c>
+      <x:c r="I30" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J30" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" s="17" t="str">
-        <x:v>architecture/released/v1.1/RFC-010_Canonical_Enterprise_Ontology_Boundary_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/GEM-001_Governance_Exception_Business_Specification_v1.1_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B31" s="17" t="str">
-        <x:v>RFC-010</x:v>
+        <x:v>GEM-001</x:v>
       </x:c>
       <x:c r="C31" s="17" t="str">
-        <x:v>RFC-010 Canonical Enterprise Ontology Boundary</x:v>
+        <x:v>GEM-001 Governance Exception Business Specification</x:v>
       </x:c>
       <x:c r="D31" s="19" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G31" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H31" s="20" t="str">
+        <x:v>50483e20d7ce808b7d3c4218097f739542123d8fd26dfcacd70091f4a7614f23</x:v>
+      </x:c>
+      <x:c r="I31" s="17" t="str">
         <x:v>1.0</x:v>
       </x:c>
-      <x:c r="E31" s="18" t="str">
-        <x:v>Frozen</x:v>
-      </x:c>
-      <x:c r="F31" s="20" t="str">
-        <x:v>38526ec74ffec1367094fc384310d00adeae58278b33dacf4ab3cec15ee36c56</x:v>
-      </x:c>
-      <x:c r="G31" s="17" t="str"/>
-      <x:c r="H31" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="J31" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" s="17" t="str">
-        <x:v>architecture/released/v1.1/RFC-011_Immutable_Record_Lifecycle_and_Currentness_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/GRM-001_Governance_Business_Capability_Specification_v1.2_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B32" s="17" t="str">
-        <x:v>RFC-011</x:v>
+        <x:v>GRM-001</x:v>
       </x:c>
       <x:c r="C32" s="17" t="str">
-        <x:v>RFC-011 Immutable Record Lifecycle and Currentness</x:v>
+        <x:v>GRM-001 Governance Business Capability Specification</x:v>
       </x:c>
       <x:c r="D32" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E32" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F32" s="20" t="str">
-        <x:v>a0bd5bb03da511a408c3d824397f1526541500e93c0cdeb8749ada4465c8b02f</x:v>
-      </x:c>
-      <x:c r="G32" s="17" t="str"/>
-      <x:c r="H32" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F32" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G32" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H32" s="20" t="str">
+        <x:v>a283a10ee9fd888576bea1171f0014cfb03d888fbc9220de82b65907660a1f75</x:v>
+      </x:c>
+      <x:c r="I32" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J32" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" s="17" t="str">
-        <x:v>architecture/released/v1.1/RFC-012_Constitutional_Reconciliation_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/KRM-001_Knowledge_Business_Capability_Specification_v1.4_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B33" s="17" t="str">
-        <x:v>RFC-012</x:v>
+        <x:v>KRM-001</x:v>
       </x:c>
       <x:c r="C33" s="17" t="str">
-        <x:v>RFC-012 Constitutional Reconciliation</x:v>
+        <x:v>KRM-001 Knowledge Business Capability Specification</x:v>
       </x:c>
       <x:c r="D33" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="E33" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F33" s="20" t="str">
-        <x:v>b7dedccedb3cdce3fed8fe46c858b5a2820b425659d96027cb6d4b925cb85f73</x:v>
-      </x:c>
-      <x:c r="G33" s="17" t="str">
-        <x:v>RFC-0001 through RFC-0009 as architecture authorities</x:v>
-      </x:c>
-      <x:c r="H33" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F33" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G33" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H33" s="20" t="str">
+        <x:v>927ff3ee653ba3d0e6865fc0a216f7603d3a681553ab5cd942cbe770c83da314</x:v>
+      </x:c>
+      <x:c r="I33" s="17" t="str">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J33" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="32" customHeight="1">
       <x:c r="A34" s="17" t="str">
-        <x:v>architecture/released/v1.1/RFC-013_Governance_Authority_and_Evaluation_Separation_v1.0_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/PAD-001_Product_Access_Protocol_Specification_v1.4_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B34" s="17" t="str">
-        <x:v>RFC-013</x:v>
+        <x:v>PAD-001</x:v>
       </x:c>
       <x:c r="C34" s="17" t="str">
-        <x:v>RFC-013 Governance Authority and Evaluation Separation</x:v>
+        <x:v>PAD-001 Product Access Protocol Specification</x:v>
       </x:c>
       <x:c r="D34" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="E34" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F34" s="20" t="str">
-        <x:v>3ea499c07d4998c542ccd5c17b02b0163f570e15d0fb3faf6fc03df31dd1b9c1</x:v>
-      </x:c>
-      <x:c r="G34" s="17" t="str">
-        <x:v>Ambiguous use of “Governance” in AEM-001 and KRM-001</x:v>
-      </x:c>
-      <x:c r="H34" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+      <x:c r="F34" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G34" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H34" s="20" t="str">
+        <x:v>41aa1ad278a5a4f804ee0f43c82cb6720853332ced4f1bb6b48381a3a327e505</x:v>
+      </x:c>
+      <x:c r="I34" s="17" t="str">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="J34" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="32" customHeight="1">
       <x:c r="A35" s="17" t="str">
-        <x:v>architecture/released/v1.1/SHA256SUMS</x:v>
+        <x:v>architecture/released/v1.1/PMM-001_Persistence_Role_Mapping_v1.0_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B35" s="17" t="str">
-        <x:v>LEGACY-SHA256SUMS</x:v>
+        <x:v>PMM-001</x:v>
       </x:c>
       <x:c r="C35" s="17" t="str">
-        <x:v>Legacy SHA-256 Checksum List</x:v>
+        <x:v>PMM-001 Persistence Role Mapping</x:v>
       </x:c>
       <x:c r="D35" s="19" t="str">
-        <x:v>v1.1</x:v>
+        <x:v>1.0</x:v>
       </x:c>
       <x:c r="E35" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F35" s="20" t="str">
-        <x:v>51f94725582a4f7fd249d647c121b4603b70cc60f61e68751dfed8e8bb933d24</x:v>
-      </x:c>
-      <x:c r="G35" s="17" t="str"/>
-      <x:c r="H35" s="17" t="str">
+      <x:c r="F35" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G35" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H35" s="20" t="str">
+        <x:v>1dda16a421594975a32bd3aa57cdf8aeb4273d1f9abb48a2f3add6f615585648</x:v>
+      </x:c>
+      <x:c r="I35" s="17" t="str"/>
+      <x:c r="J35" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="32" customHeight="1">
       <x:c r="A36" s="17" t="str">
-        <x:v>architecture/released/v1.1/SRM-001_Semantic_Resolution_Business_Capability_Specification_v2.1_FROZEN.docx</x:v>
+        <x:v>architecture/released/v1.1/README.md</x:v>
       </x:c>
       <x:c r="B36" s="17" t="str">
-        <x:v>SRM-001</x:v>
+        <x:v>RELEASE-README</x:v>
       </x:c>
       <x:c r="C36" s="17" t="str">
-        <x:v>SRM-001 Semantic Resolution Business Capability Specification</x:v>
+        <x:v>Architecture Release Baseline README</x:v>
       </x:c>
       <x:c r="D36" s="19" t="str">
-        <x:v>2.1</x:v>
+        <x:v>v1.1</x:v>
       </x:c>
       <x:c r="E36" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F36" s="20" t="str">
-        <x:v>004e3861626a8bcace8524c7f2aa1573938ec9840bacd45088efaa38c8fa0eb7</x:v>
-      </x:c>
-      <x:c r="G36" s="17" t="str">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="H36" s="17" t="str">
+      <x:c r="F36" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G36" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H36" s="20" t="str">
+        <x:v>0b01420bb87741ec1fbcdfcdcb0a7ff89e521652bb20008fbc77e29d41ddcb1f</x:v>
+      </x:c>
+      <x:c r="I36" s="17" t="str"/>
+      <x:c r="J36" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="32" customHeight="1">
       <x:c r="A37" s="17" t="str">
-        <x:v>architecture/released/v1.1/TAS-001_Part1_YC_Prototype_Technology_Architecture.docx</x:v>
+        <x:v>architecture/released/v1.1/RELEASE-READINESS-REPORT-v1.2_FROZEN.md</x:v>
       </x:c>
       <x:c r="B37" s="17" t="str">
-        <x:v>TAS-001 Part 1</x:v>
+        <x:v>Release Readiness Report</x:v>
       </x:c>
       <x:c r="C37" s="17" t="str">
-        <x:v>TAS-001 Part1 YC Prototype Technology Architecture</x:v>
+        <x:v>RELEASE-READINESS-REPORT-v1.2</x:v>
       </x:c>
       <x:c r="D37" s="19" t="str">
-        <x:v>1.0</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="E37" s="18" t="str">
-        <x:v>Development</x:v>
-      </x:c>
-      <x:c r="F37" s="20" t="str">
-        <x:v>4706af128a2a978ef4df21e008d5d92b968efca187ababa31769a1ccc0fd6ca3</x:v>
-      </x:c>
-      <x:c r="G37" s="17" t="str"/>
-      <x:c r="H37" s="17" t="str">
-        <x:v>Architecture Registry v1.1 release decision</x:v>
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F37" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G37" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H37" s="20" t="str">
+        <x:v>b916563c615a02d2808892394c3d8754f3707e0739b88061b231657457281ade</x:v>
+      </x:c>
+      <x:c r="I37" s="17" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="J37" s="17" t="str">
+        <x:v>ECOM Architecture Governance release approval — 2026-08-08</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="32" customHeight="1">
       <x:c r="A38" s="17" t="str">
-        <x:v>architecture/released/v1.1/The Constitutional Theory of Enterprise Cognition - Version 1.0.docx</x:v>
+        <x:v>architecture/released/v1.1/RFC-010_Canonical_Enterprise_Ontology_Boundary_v1.0_FROZEN.docx</x:v>
       </x:c>
       <x:c r="B38" s="17" t="str">
-        <x:v>Enterprise Constitution</x:v>
+        <x:v>RFC-010</x:v>
       </x:c>
       <x:c r="C38" s="17" t="str">
-        <x:v>The Constitutional Theory of Enterprise Cognition</x:v>
+        <x:v>RFC-010 Canonical Enterprise Ontology Boundary</x:v>
       </x:c>
       <x:c r="D38" s="19" t="str">
         <x:v>1.0</x:v>
@@ -1256,23 +1470,275 @@
       <x:c r="E38" s="18" t="str">
         <x:v>Frozen</x:v>
       </x:c>
-      <x:c r="F38" s="20" t="str">
+      <x:c r="F38" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G38" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H38" s="20" t="str">
+        <x:v>38526ec74ffec1367094fc384310d00adeae58278b33dacf4ab3cec15ee36c56</x:v>
+      </x:c>
+      <x:c r="I38" s="17" t="str"/>
+      <x:c r="J38" s="17" t="str">
+        <x:v>Architecture Registry v1.1 release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="32" customHeight="1">
+      <x:c r="A39" s="17" t="str">
+        <x:v>architecture/released/v1.1/RFC-011_Immutable_Record_Lifecycle_and_Currentness_v1.0_FROZEN.docx</x:v>
+      </x:c>
+      <x:c r="B39" s="17" t="str">
+        <x:v>RFC-011</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="str">
+        <x:v>RFC-011 Immutable Record Lifecycle and Currentness</x:v>
+      </x:c>
+      <x:c r="D39" s="19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F39" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G39" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H39" s="20" t="str">
+        <x:v>a0bd5bb03da511a408c3d824397f1526541500e93c0cdeb8749ada4465c8b02f</x:v>
+      </x:c>
+      <x:c r="I39" s="17" t="str"/>
+      <x:c r="J39" s="17" t="str">
+        <x:v>Architecture Registry v1.1 release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="32" customHeight="1">
+      <x:c r="A40" s="17" t="str">
+        <x:v>architecture/released/v1.1/RFC-012_Constitutional_Reconciliation_v1.0_FROZEN.docx</x:v>
+      </x:c>
+      <x:c r="B40" s="17" t="str">
+        <x:v>RFC-012</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="str">
+        <x:v>RFC-012 Constitutional Reconciliation</x:v>
+      </x:c>
+      <x:c r="D40" s="19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F40" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G40" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H40" s="20" t="str">
+        <x:v>b7dedccedb3cdce3fed8fe46c858b5a2820b425659d96027cb6d4b925cb85f73</x:v>
+      </x:c>
+      <x:c r="I40" s="17" t="str">
+        <x:v>RFC-0001 through RFC-0009 as architecture authorities</x:v>
+      </x:c>
+      <x:c r="J40" s="17" t="str">
+        <x:v>Architecture Registry v1.1 release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="32" customHeight="1">
+      <x:c r="A41" s="17" t="str">
+        <x:v>architecture/released/v1.1/RFC-013_Governance_Authority_and_Evaluation_Separation_v1.1_FROZEN.docx</x:v>
+      </x:c>
+      <x:c r="B41" s="17" t="str">
+        <x:v>RFC-013</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="str">
+        <x:v>RFC-013 Governance Authority and Evaluation Separation</x:v>
+      </x:c>
+      <x:c r="D41" s="19" t="str">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F41" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G41" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H41" s="20" t="str">
+        <x:v>b4a8999419b43b78a61982edae6c9c2d57bdac4a55372cd4cad7997c64065797</x:v>
+      </x:c>
+      <x:c r="I41" s="17" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="J41" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="32" customHeight="1">
+      <x:c r="A42" s="17" t="str">
+        <x:v>architecture/released/v1.1/RND-001_Architecture_Registry_Normalization_v1.0_FROZEN.md</x:v>
+      </x:c>
+      <x:c r="B42" s="17" t="str">
+        <x:v>RND-001</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="str">
+        <x:v>RND-001 Architecture Registry Normalization</x:v>
+      </x:c>
+      <x:c r="D42" s="19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F42" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G42" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H42" s="20" t="str">
+        <x:v>2bbfa3bc5815d5eb43fe592ff28e568d7264443139fb9c0c99c1674031a436b2</x:v>
+      </x:c>
+      <x:c r="I42" s="17" t="str"/>
+      <x:c r="J42" s="17" t="str">
+        <x:v>RND-001 registry normalization approval — 2026-08-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="32" customHeight="1">
+      <x:c r="A43" s="17" t="str">
+        <x:v>architecture/released/v1.1/SHA256SUMS</x:v>
+      </x:c>
+      <x:c r="B43" s="17" t="str">
+        <x:v>LEGACY-SHA256SUMS</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="str">
+        <x:v>Legacy SHA-256 Checksum List</x:v>
+      </x:c>
+      <x:c r="D43" s="19" t="str">
+        <x:v>v1.1</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F43" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G43" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H43" s="20" t="str">
+        <x:v>395eab5184c1c88841d4a31e15bd06ee12057ce759d5006f32fbdd46a6d9a0dd</x:v>
+      </x:c>
+      <x:c r="I43" s="17" t="str"/>
+      <x:c r="J43" s="17" t="str">
+        <x:v>Architecture Registry v1.1 release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="32" customHeight="1">
+      <x:c r="A44" s="17" t="str">
+        <x:v>architecture/released/v1.1/SRM-001_Semantic_Resolution_Business_Capability_Specification_v2.2_FROZEN.docx</x:v>
+      </x:c>
+      <x:c r="B44" s="17" t="str">
+        <x:v>SRM-001</x:v>
+      </x:c>
+      <x:c r="C44" s="17" t="str">
+        <x:v>SRM-001 Semantic Resolution Business Capability Specification</x:v>
+      </x:c>
+      <x:c r="D44" s="19" t="str">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="E44" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F44" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G44" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H44" s="20" t="str">
+        <x:v>367f12f3fd9231a0edb7ce99951e6d007fa492d04f105b17cd30173d4b1c9923</x:v>
+      </x:c>
+      <x:c r="I44" s="17" t="str">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="J44" s="17" t="str">
+        <x:v>DRR-001 dependency reconciliation approval — 2026-08-08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="32" customHeight="1">
+      <x:c r="A45" s="17" t="str">
+        <x:v>architecture/released/v1.1/TAS-001_Part1_YC_Prototype_Technology_Architecture.docx</x:v>
+      </x:c>
+      <x:c r="B45" s="17" t="str">
+        <x:v>TAS-001 Part 1</x:v>
+      </x:c>
+      <x:c r="C45" s="17" t="str">
+        <x:v>TAS-001 Part1 YC Prototype Technology Architecture</x:v>
+      </x:c>
+      <x:c r="D45" s="19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E45" s="18" t="str">
+        <x:v>Development</x:v>
+      </x:c>
+      <x:c r="F45" s="18" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G45" s="18" t="str">
+        <x:v>NON-AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H45" s="20" t="str">
+        <x:v>4706af128a2a978ef4df21e008d5d92b968efca187ababa31769a1ccc0fd6ca3</x:v>
+      </x:c>
+      <x:c r="I45" s="17" t="str"/>
+      <x:c r="J45" s="17" t="str">
+        <x:v>Architecture Registry v1.1 release decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="32" customHeight="1">
+      <x:c r="A46" s="17" t="str">
+        <x:v>architecture/released/v1.1/The Constitutional Theory of Enterprise Cognition - Version 1.0.docx</x:v>
+      </x:c>
+      <x:c r="B46" s="17" t="str">
+        <x:v>Enterprise Constitution</x:v>
+      </x:c>
+      <x:c r="C46" s="17" t="str">
+        <x:v>The Constitutional Theory of Enterprise Cognition</x:v>
+      </x:c>
+      <x:c r="D46" s="19" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E46" s="18" t="str">
+        <x:v>Frozen</x:v>
+      </x:c>
+      <x:c r="F46" s="18" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G46" s="18" t="str">
+        <x:v>AUTHORITATIVE</x:v>
+      </x:c>
+      <x:c r="H46" s="20" t="str">
         <x:v>961ae3460c2c8d032dedff055ea586f373d77fc659cf9e493571aa4969738217</x:v>
       </x:c>
-      <x:c r="G38" s="17" t="str"/>
-      <x:c r="H38" s="17" t="str">
+      <x:c r="I46" s="17" t="str"/>
+      <x:c r="J46" s="17" t="str">
         <x:v>Architecture Registry v1.1 release decision</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="E3:H3"/>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+    <x:mergeCell ref="E3:J3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5bb2826d6f7491a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5555b8dc52034915"/>
   </x:tableParts>
 </x:worksheet>
 </file>